--- a/config/yunying/skyscraper_tasks.xlsx
+++ b/config/yunying/skyscraper_tasks.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>本日25階層に到達</t>
+          <t>今天到达25层</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>本日75階層に到達</t>
+          <t>今天到达75层</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>本日累計800Pt獲得</t>
+          <t>今日累计获得800pt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>本日累計1600Pt獲得</t>
+          <t>今日累计获得1600pt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>本日完璧建設評価を8回獲得</t>
+          <t>今天获得8次完美建设评价</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>本日完璧建設評価を20回獲得</t>
+          <t>今天获得20次完美建设评价</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
